--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260224_202423.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
